--- a/templates/07_Rent_Template.xlsx
+++ b/templates/07_Rent_Template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rent" sheetId="1" r:id="R162cb331ecc54e8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rent" sheetId="1" r:id="R9e422d3791664b1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,10 +265,10 @@
         <x:v>Yo-Chi Albert St</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:v>11431.6</x:v>
+        <x:v>11831.71</x:v>
       </x:c>
       <x:c r="C2" s="7" t="n">
-        <x:v>5833.59</x:v>
+        <x:v>6037.77</x:v>
       </x:c>
       <x:c r="D2" s="7" t="n">
         <x:v>514594.6</x:v>
@@ -285,10 +285,10 @@
         <x:v>Yo-Chi Balaclava</x:v>
       </x:c>
       <x:c r="B3" s="7" t="n">
-        <x:v>10902.99</x:v>
+        <x:v>11284.59</x:v>
       </x:c>
       <x:c r="C3" s="7" t="n">
-        <x:v>616.81</x:v>
+        <x:v>638.4</x:v>
       </x:c>
       <x:c r="D3" s="7" t="n">
         <x:v>186484.58</x:v>
@@ -305,10 +305,10 @@
         <x:v>Yo-Chi Barangaroo</x:v>
       </x:c>
       <x:c r="B4" s="7" t="n">
-        <x:v>36627.27</x:v>
+        <x:v>37909.22</x:v>
       </x:c>
       <x:c r="C4" s="7" t="n">
-        <x:v>27794.38</x:v>
+        <x:v>28767.18</x:v>
       </x:c>
       <x:c r="D4" s="7" t="n">
         <x:v>529983.96</x:v>
@@ -325,10 +325,10 @@
         <x:v>Yo-Chi Bondi</x:v>
       </x:c>
       <x:c r="B5" s="7" t="n">
-        <x:v>20413.39</x:v>
+        <x:v>21127.86</x:v>
       </x:c>
       <x:c r="C5" s="7" t="n">
-        <x:v>188.52</x:v>
+        <x:v>195.12</x:v>
       </x:c>
       <x:c r="D5" s="7" t="n">
         <x:v>362464.58</x:v>
@@ -345,10 +345,10 @@
         <x:v>Yo-Chi Bondi Junction</x:v>
       </x:c>
       <x:c r="B6" s="7" t="n">
-        <x:v>10444.44</x:v>
+        <x:v>10810</x:v>
       </x:c>
       <x:c r="C6" s="7" t="n">
-        <x:v>1657.26</x:v>
+        <x:v>1715.26</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
         <x:v>187634.64</x:v>
@@ -365,10 +365,10 @@
         <x:v>Yo-Chi Brighton</x:v>
       </x:c>
       <x:c r="B7" s="7" t="n">
-        <x:v>7004.14</x:v>
+        <x:v>7249.28</x:v>
       </x:c>
       <x:c r="C7" s="7" t="n">
-        <x:v>850.73</x:v>
+        <x:v>880.51</x:v>
       </x:c>
       <x:c r="D7" s="7" t="n">
         <x:v>238146.06</x:v>
@@ -385,10 +385,10 @@
         <x:v>Yo-Chi Broadbeach</x:v>
       </x:c>
       <x:c r="B8" s="7" t="n">
-        <x:v>12562.74</x:v>
+        <x:v>13002.44</x:v>
       </x:c>
       <x:c r="C8" s="7" t="n">
-        <x:v>1309.68</x:v>
+        <x:v>1355.52</x:v>
       </x:c>
       <x:c r="D8" s="7" t="n">
         <x:v>368743.99</x:v>
@@ -405,10 +405,10 @@
         <x:v>Yo-Chi Bulimba</x:v>
       </x:c>
       <x:c r="B9" s="7" t="n">
-        <x:v>5592.51</x:v>
+        <x:v>5788.25</x:v>
       </x:c>
       <x:c r="C9" s="7" t="n">
-        <x:v>3133.2</x:v>
+        <x:v>3242.86</x:v>
       </x:c>
       <x:c r="D9" s="7" t="n">
         <x:v>243592.46</x:v>
@@ -425,10 +425,10 @@
         <x:v>Yo-Chi Burleigh</x:v>
       </x:c>
       <x:c r="B10" s="7" t="n">
-        <x:v>10459.48</x:v>
+        <x:v>10825.56</x:v>
       </x:c>
       <x:c r="C10" s="7" t="n">
-        <x:v>57.81</x:v>
+        <x:v>59.83</x:v>
       </x:c>
       <x:c r="D10" s="7" t="n">
         <x:v>288559.48</x:v>
@@ -445,10 +445,10 @@
         <x:v>Yo-Chi Burwood</x:v>
       </x:c>
       <x:c r="B11" s="7" t="n">
-        <x:v>14206.99</x:v>
+        <x:v>14704.23</x:v>
       </x:c>
       <x:c r="C11" s="7" t="n">
-        <x:v>968.75</x:v>
+        <x:v>1002.66</x:v>
       </x:c>
       <x:c r="D11" s="7" t="n">
         <x:v>224044.25</x:v>
@@ -465,10 +465,10 @@
         <x:v>Yo-Chi Carlton</x:v>
       </x:c>
       <x:c r="B12" s="7" t="n">
-        <x:v>11259.26</x:v>
+        <x:v>11653.33</x:v>
       </x:c>
       <x:c r="C12" s="7" t="n">
-        <x:v>659.48</x:v>
+        <x:v>682.56</x:v>
       </x:c>
       <x:c r="D12" s="7" t="n">
         <x:v>536289.65</x:v>
@@ -485,10 +485,10 @@
         <x:v>Yo-Chi Castle Towers</x:v>
       </x:c>
       <x:c r="B13" s="7" t="n">
-        <x:v>10421.14</x:v>
+        <x:v>10785.88</x:v>
       </x:c>
       <x:c r="C13" s="7" t="n">
-        <x:v>1841.57</x:v>
+        <x:v>1906.02</x:v>
       </x:c>
       <x:c r="D13" s="7" t="n">
         <x:v>206244.17</x:v>
@@ -505,10 +505,10 @@
         <x:v>Yo-Chi Chadstone</x:v>
       </x:c>
       <x:c r="B14" s="7" t="n">
-        <x:v>19030.77</x:v>
+        <x:v>19696.85</x:v>
       </x:c>
       <x:c r="C14" s="7" t="n">
-        <x:v>4634.82</x:v>
+        <x:v>4797.04</x:v>
       </x:c>
       <x:c r="D14" s="7" t="n">
         <x:v>223197.61</x:v>
@@ -522,1121 +522,1101 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>Yo-Chi Charlestown</x:v>
+        <x:v>Yo-Chi Chatswood</x:v>
       </x:c>
       <x:c r="B15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>17250</x:v>
       </x:c>
       <x:c r="C15" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="7" t="n">
-        <x:v>678.48</x:v>
+        <x:v>223171.2</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>Yo-Chi Chatswood</x:v>
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
       </x:c>
       <x:c r="B16" s="7" t="n">
-        <x:v>16666.67</x:v>
+        <x:v>7128.11</x:v>
       </x:c>
       <x:c r="C16" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1817.09</x:v>
       </x:c>
       <x:c r="D16" s="7" t="n">
-        <x:v>223171.2</x:v>
+        <x:v>202423.3</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.9400000000000001</x:v>
       </x:c>
       <x:c r="F16" s="7" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.44</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+        <x:v>Yo-Chi Chippendale</x:v>
       </x:c>
       <x:c r="B17" s="7" t="n">
-        <x:v>6887.06</x:v>
+        <x:v>7858.33</x:v>
       </x:c>
       <x:c r="C17" s="7" t="n">
-        <x:v>1755.64</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="7" t="n">
-        <x:v>202423.3</x:v>
+        <x:v>98817.98</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>0.9400000000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="7" t="n">
-        <x:v>0.44</x:v>
+        <x:v>0.52</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>Yo-Chi Chippendale</x:v>
+        <x:v>Yo-Chi Circular Quay</x:v>
       </x:c>
       <x:c r="B18" s="7" t="n">
-        <x:v>7592.59</x:v>
+        <x:v>18449.88</x:v>
       </x:c>
       <x:c r="C18" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3781.13</x:v>
       </x:c>
       <x:c r="D18" s="7" t="n">
-        <x:v>98817.98</x:v>
+        <x:v>374399.23</x:v>
       </x:c>
       <x:c r="E18" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="F18" s="7" t="n">
-        <x:v>0.52</x:v>
+        <x:v>0.13999999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>Yo-Chi Circular Quay</x:v>
+        <x:v>Yo-Chi Claremont</x:v>
       </x:c>
       <x:c r="B19" s="7" t="n">
-        <x:v>17825.97</x:v>
+        <x:v>12124.84</x:v>
       </x:c>
       <x:c r="C19" s="7" t="n">
-        <x:v>3653.27</x:v>
+        <x:v>5116.73</x:v>
       </x:c>
       <x:c r="D19" s="7" t="n">
-        <x:v>374399.23</x:v>
+        <x:v>232194.81</x:v>
       </x:c>
       <x:c r="E19" s="7" t="n">
-        <x:v>2.79</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="7" t="n">
-        <x:v>0.13999999999999999</x:v>
+        <x:v>0.36</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>Yo-Chi Claremont</x:v>
+        <x:v>Yo-Chi Cockburn Central</x:v>
       </x:c>
       <x:c r="B20" s="7" t="n">
-        <x:v>11714.82</x:v>
+        <x:v>10396.12</x:v>
       </x:c>
       <x:c r="C20" s="7" t="n">
-        <x:v>4943.7</x:v>
+        <x:v>5017.03</x:v>
       </x:c>
       <x:c r="D20" s="7" t="n">
-        <x:v>232194.81</x:v>
+        <x:v>423004.86</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="F20" s="7" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.16</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
-        <x:v>Yo-Chi Cockburn Central</x:v>
+        <x:v>Yo-Chi Coogee</x:v>
       </x:c>
       <x:c r="B21" s="7" t="n">
-        <x:v>10044.56</x:v>
+        <x:v>12558.01</x:v>
       </x:c>
       <x:c r="C21" s="7" t="n">
-        <x:v>4847.37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="7" t="n">
-        <x:v>423004.86</x:v>
+        <x:v>366782.08</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>2.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F21" s="7" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.19</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>Yo-Chi Coogee</x:v>
+        <x:v>Yo-Chi Cronulla</x:v>
       </x:c>
       <x:c r="B22" s="7" t="n">
-        <x:v>12133.34</x:v>
+        <x:v>19371.54</x:v>
       </x:c>
       <x:c r="C22" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4893.91</x:v>
       </x:c>
       <x:c r="D22" s="7" t="n">
-        <x:v>366782.08</x:v>
+        <x:v>342173.96</x:v>
       </x:c>
       <x:c r="E22" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="F22" s="7" t="n">
-        <x:v>0.19</x:v>
+        <x:v>0.21</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
-        <x:v>Yo-Chi Cronulla</x:v>
+        <x:v>Yo-Chi Currambine</x:v>
       </x:c>
       <x:c r="B23" s="7" t="n">
-        <x:v>18716.46</x:v>
+        <x:v>7674.67</x:v>
       </x:c>
       <x:c r="C23" s="7" t="n">
-        <x:v>4728.42</x:v>
+        <x:v>1475.41</x:v>
       </x:c>
       <x:c r="D23" s="7" t="n">
-        <x:v>342173.96</x:v>
+        <x:v>373094.48</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
-        <x:v>1.97</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="F23" s="7" t="n">
-        <x:v>0.21</x:v>
+        <x:v>0.22999999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
-        <x:v>Yo-Chi Currambine</x:v>
+        <x:v>Yo-Chi Double Bay</x:v>
       </x:c>
       <x:c r="B24" s="7" t="n">
-        <x:v>7415.14</x:v>
+        <x:v>20178.52</x:v>
       </x:c>
       <x:c r="C24" s="7" t="n">
-        <x:v>1425.52</x:v>
+        <x:v>2395.52</x:v>
       </x:c>
       <x:c r="D24" s="7" t="n">
-        <x:v>373094.48</x:v>
+        <x:v>187627.97</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
-        <x:v>1.13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F24" s="7" t="n">
-        <x:v>0.22999999999999998</x:v>
+        <x:v>0.38</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="7" t="str">
-        <x:v>Yo-Chi Double Bay</x:v>
+        <x:v>Yo-Chi Eastland</x:v>
       </x:c>
       <x:c r="B25" s="7" t="n">
-        <x:v>19496.15</x:v>
+        <x:v>14377.45</x:v>
       </x:c>
       <x:c r="C25" s="7" t="n">
-        <x:v>2314.51</x:v>
+        <x:v>4644.63</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>187627.97</x:v>
+        <x:v>312470.86</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="F25" s="7" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.41000000000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="7" t="str">
-        <x:v>Yo-Chi Eastland</x:v>
+        <x:v>Yo-Chi Forrest Chase</x:v>
       </x:c>
       <x:c r="B26" s="7" t="n">
-        <x:v>13891.26</x:v>
+        <x:v>12401.07</x:v>
       </x:c>
       <x:c r="C26" s="7" t="n">
-        <x:v>4487.57</x:v>
+        <x:v>1925.6</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>312470.86</x:v>
+        <x:v>483706.98</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
-        <x:v>0.5</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="F26" s="7" t="n">
-        <x:v>0.41000000000000003</x:v>
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
-        <x:v>Yo-Chi Forrest Chase</x:v>
+        <x:v>Yo-Chi Fremantle</x:v>
       </x:c>
       <x:c r="B27" s="7" t="n">
-        <x:v>11981.71</x:v>
+        <x:v>7576.36</x:v>
       </x:c>
       <x:c r="C27" s="7" t="n">
-        <x:v>1860.48</x:v>
+        <x:v>2708.07</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
-        <x:v>483706.98</x:v>
+        <x:v>339131.43</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>2.73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="7" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.37</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="7" t="str">
-        <x:v>Yo-Chi Fremantle</x:v>
+        <x:v>Yo-Chi Gasworks</x:v>
       </x:c>
       <x:c r="B28" s="7" t="n">
-        <x:v>7320.15</x:v>
+        <x:v>20637.4</x:v>
       </x:c>
       <x:c r="C28" s="7" t="n">
-        <x:v>2616.49</x:v>
+        <x:v>4916.14</x:v>
       </x:c>
       <x:c r="D28" s="7" t="n">
-        <x:v>339131.43</x:v>
+        <x:v>271241.7</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="F28" s="7" t="n">
-        <x:v>0.37</x:v>
+        <x:v>0.21</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
-        <x:v>Yo-Chi Gasworks</x:v>
+        <x:v>Yo-Chi George St</x:v>
       </x:c>
       <x:c r="B29" s="7" t="n">
-        <x:v>19939.52</x:v>
+        <x:v>52702.81</x:v>
       </x:c>
       <x:c r="C29" s="7" t="n">
-        <x:v>4749.89</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="7" t="n">
-        <x:v>271241.7</x:v>
+        <x:v>473603.32</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>0.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="7" t="n">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="7" t="str">
-        <x:v>Yo-Chi George St</x:v>
+        <x:v>Yo-Chi Glenelg</x:v>
       </x:c>
       <x:c r="B30" s="7" t="n">
-        <x:v>50920.59</x:v>
+        <x:v>10990.23</x:v>
       </x:c>
       <x:c r="C30" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2170.29</x:v>
       </x:c>
       <x:c r="D30" s="7" t="n">
-        <x:v>473603.32</x:v>
+        <x:v>320701.32</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="7" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.35000000000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="7" t="str">
-        <x:v>Yo-Chi Glenelg</x:v>
+        <x:v>Yo-Chi Gouger St</x:v>
       </x:c>
       <x:c r="B31" s="7" t="n">
-        <x:v>10618.58</x:v>
+        <x:v>15999.36</x:v>
       </x:c>
       <x:c r="C31" s="7" t="n">
-        <x:v>2096.9</x:v>
+        <x:v>3117.25</x:v>
       </x:c>
       <x:c r="D31" s="7" t="n">
-        <x:v>320701.32</x:v>
+        <x:v>240727.21</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F31" s="7" t="n">
-        <x:v>0.35000000000000003</x:v>
+        <x:v>0.47000000000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="7" t="str">
-        <x:v>Yo-Chi Gouger St</x:v>
+        <x:v>Yo-Chi Harbour Town</x:v>
       </x:c>
       <x:c r="B32" s="7" t="n">
-        <x:v>15458.32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="7" t="n">
-        <x:v>3011.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="7" t="n">
-        <x:v>240727.21</x:v>
+        <x:v>21217.6</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="7" t="n">
-        <x:v>0.47000000000000003</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
-        <x:v>Yo-Chi Harbour Town</x:v>
+        <x:v>Yo-Chi Hawthorn</x:v>
       </x:c>
       <x:c r="B33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>21391.17</x:v>
       </x:c>
       <x:c r="C33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3166.04</x:v>
       </x:c>
       <x:c r="D33" s="7" t="n">
-        <x:v>21217.6</x:v>
+        <x:v>354405.19</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
-        <x:v>Yo-Chi Hawthorn</x:v>
+        <x:v>Yo-Chi Henley Beach</x:v>
       </x:c>
       <x:c r="B34" s="7" t="n">
-        <x:v>20667.8</x:v>
+        <x:v>9239.32</x:v>
       </x:c>
       <x:c r="C34" s="7" t="n">
-        <x:v>3058.98</x:v>
+        <x:v>2540.08</x:v>
       </x:c>
       <x:c r="D34" s="7" t="n">
-        <x:v>354405.19</x:v>
+        <x:v>235516.08</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F34" s="7" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.52</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="7" t="str">
-        <x:v>Yo-Chi Henley Beach</x:v>
+        <x:v>Yo-Chi Highgate</x:v>
       </x:c>
       <x:c r="B35" s="7" t="n">
-        <x:v>8926.88</x:v>
+        <x:v>12081.6</x:v>
       </x:c>
       <x:c r="C35" s="7" t="n">
-        <x:v>2454.18</x:v>
+        <x:v>394.38</x:v>
       </x:c>
       <x:c r="D35" s="7" t="n">
-        <x:v>235516.08</x:v>
+        <x:v>261354.84</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F35" s="7" t="n">
-        <x:v>0.52</x:v>
+        <x:v>0.43</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="str">
-        <x:v>Yo-Chi Highgate</x:v>
+        <x:v>Yo-Chi Highpoint</x:v>
       </x:c>
       <x:c r="B36" s="7" t="n">
-        <x:v>11673.04</x:v>
+        <x:v>13737.23</x:v>
       </x:c>
       <x:c r="C36" s="7" t="n">
-        <x:v>381.04</x:v>
+        <x:v>3764.5</x:v>
       </x:c>
       <x:c r="D36" s="7" t="n">
-        <x:v>261354.84</x:v>
+        <x:v>345170.86</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>2.4</x:v>
+        <x:v>1.1900000000000002</x:v>
       </x:c>
       <x:c r="F36" s="7" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.26</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
-        <x:v>Yo-Chi Highpoint</x:v>
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
-        <x:v>13272.69</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="C37" s="7" t="n">
-        <x:v>3637.2</x:v>
+        <x:v>352.61</x:v>
       </x:c>
       <x:c r="D37" s="7" t="n">
-        <x:v>345170.86</x:v>
+        <x:v>42191.63</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>1.1900000000000002</x:v>
+        <x:v>3.2199999999999998</x:v>
       </x:c>
       <x:c r="F37" s="7" t="n">
-        <x:v>0.26</x:v>
+        <x:v>1.21</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
-        <x:v>Yo-Chi Indooroopilly</x:v>
+        <x:v>Yo-Chi Karrinyup</x:v>
       </x:c>
       <x:c r="B38" s="7" t="n">
-        <x:v>1111.11</x:v>
+        <x:v>26807.9</x:v>
       </x:c>
       <x:c r="C38" s="7" t="n">
-        <x:v>340.69</x:v>
+        <x:v>519.2</x:v>
       </x:c>
       <x:c r="D38" s="7" t="n">
-        <x:v>42191.63</x:v>
+        <x:v>607768.33</x:v>
       </x:c>
       <x:c r="E38" s="7" t="n">
-        <x:v>3.2199999999999998</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="F38" s="7" t="n">
-        <x:v>1.21</x:v>
+        <x:v>0.22999999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="7" t="str">
-        <x:v>Yo-Chi Karrinyup</x:v>
+        <x:v>Yo-Chi Kawana Waters</x:v>
       </x:c>
       <x:c r="B39" s="7" t="n">
-        <x:v>25901.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="7" t="n">
-        <x:v>501.64</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="7" t="n">
-        <x:v>607768.33</x:v>
+        <x:v>16607.32</x:v>
       </x:c>
       <x:c r="E39" s="7" t="n">
-        <x:v>2.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F39" s="7" t="n">
-        <x:v>0.22999999999999998</x:v>
+        <x:v>0.98</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="7" t="str">
-        <x:v>Yo-Chi Kawana Waters</x:v>
+        <x:v>Yo-Chi Lane Cove</x:v>
       </x:c>
       <x:c r="B40" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>12908.69</x:v>
       </x:c>
       <x:c r="C40" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1003.53</x:v>
       </x:c>
       <x:c r="D40" s="7" t="n">
-        <x:v>16607.32</x:v>
+        <x:v>197028.51</x:v>
       </x:c>
       <x:c r="E40" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F40" s="7" t="n">
-        <x:v>0.98</x:v>
+        <x:v>0.61</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
-        <x:v>Yo-Chi Lane Cove</x:v>
+        <x:v>Yo-Chi Leederville</x:v>
       </x:c>
       <x:c r="B41" s="7" t="n">
-        <x:v>12472.16</x:v>
+        <x:v>11337.96</x:v>
       </x:c>
       <x:c r="C41" s="7" t="n">
-        <x:v>969.59</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D41" s="7" t="n">
-        <x:v>197028.51</x:v>
+        <x:v>308470.39</x:v>
       </x:c>
       <x:c r="E41" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F41" s="7" t="n">
-        <x:v>0.61</x:v>
+        <x:v>0.54</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="7" t="str">
-        <x:v>Yo-Chi Leederville</x:v>
+        <x:v>Yo-Chi Macquarie</x:v>
       </x:c>
       <x:c r="B42" s="7" t="n">
-        <x:v>10954.55</x:v>
+        <x:v>21586.02</x:v>
       </x:c>
       <x:c r="C42" s="7" t="n">
-        <x:v>2377.78</x:v>
+        <x:v>2557.51</x:v>
       </x:c>
       <x:c r="D42" s="7" t="n">
-        <x:v>308470.39</x:v>
+        <x:v>365624.38</x:v>
       </x:c>
       <x:c r="E42" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="F42" s="7" t="n">
-        <x:v>0.54</x:v>
+        <x:v>0.16999999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
-        <x:v>Yo-Chi Macquarie</x:v>
+        <x:v>Yo-Chi Malvern</x:v>
       </x:c>
       <x:c r="B43" s="7" t="n">
-        <x:v>20856.06</x:v>
+        <x:v>11840.4</x:v>
       </x:c>
       <x:c r="C43" s="7" t="n">
-        <x:v>2471.02</x:v>
+        <x:v>436.23</x:v>
       </x:c>
       <x:c r="D43" s="7" t="n">
-        <x:v>365624.38</x:v>
+        <x:v>220292.96</x:v>
       </x:c>
       <x:c r="E43" s="7" t="n">
-        <x:v>1.76</x:v>
+        <x:v>2.0500000000000003</x:v>
       </x:c>
       <x:c r="F43" s="7" t="n">
-        <x:v>0.16999999999999998</x:v>
+        <x:v>0.59</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="str">
-        <x:v>Yo-Chi Malvern</x:v>
+        <x:v>Yo-Chi Mandurah</x:v>
       </x:c>
       <x:c r="B44" s="7" t="n">
-        <x:v>11440</x:v>
+        <x:v>4160.69</x:v>
       </x:c>
       <x:c r="C44" s="7" t="n">
-        <x:v>421.48</x:v>
+        <x:v>1245.27</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
-        <x:v>220292.96</x:v>
+        <x:v>253875.47</x:v>
       </x:c>
       <x:c r="E44" s="7" t="n">
-        <x:v>2.0500000000000003</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F44" s="7" t="n">
-        <x:v>0.59</x:v>
+        <x:v>0.38</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
-        <x:v>Yo-Chi Mandurah</x:v>
+        <x:v>Yo-Chi Manly</x:v>
       </x:c>
       <x:c r="B45" s="7" t="n">
-        <x:v>4019.99</x:v>
+        <x:v>21181.15</x:v>
       </x:c>
       <x:c r="C45" s="7" t="n">
-        <x:v>1203.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>253875.47</x:v>
+        <x:v>397816.06</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F45" s="7" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.16</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="str">
-        <x:v>Yo-Chi Manly</x:v>
+        <x:v>Yo-Chi Mt Gravatt</x:v>
       </x:c>
       <x:c r="B46" s="7" t="n">
-        <x:v>20464.88</x:v>
+        <x:v>13922.15</x:v>
       </x:c>
       <x:c r="C46" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>815.16</x:v>
       </x:c>
       <x:c r="D46" s="7" t="n">
-        <x:v>397816.06</x:v>
+        <x:v>435252.04</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4.21</x:v>
       </x:c>
       <x:c r="F46" s="7" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.32</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
-        <x:v>Yo-Chi Mt Gravatt</x:v>
+        <x:v>Yo-Chi Newtown</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
-        <x:v>13451.35</x:v>
+        <x:v>12953.2</x:v>
       </x:c>
       <x:c r="C47" s="7" t="n">
-        <x:v>787.59</x:v>
+        <x:v>1862.39</x:v>
       </x:c>
       <x:c r="D47" s="7" t="n">
-        <x:v>435252.04</x:v>
+        <x:v>369322.21</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>4.21</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="F47" s="7" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.52</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="str">
-        <x:v>Yo-Chi Newtown</x:v>
+        <x:v>Yo-Chi Noosa</x:v>
       </x:c>
       <x:c r="B48" s="7" t="n">
-        <x:v>12515.17</x:v>
+        <x:v>17435.84</x:v>
       </x:c>
       <x:c r="C48" s="7" t="n">
-        <x:v>1799.41</x:v>
+        <x:v>1854.64</x:v>
       </x:c>
       <x:c r="D48" s="7" t="n">
-        <x:v>369322.21</x:v>
+        <x:v>346770.82</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>2.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F48" s="7" t="n">
-        <x:v>0.52</x:v>
+        <x:v>0.16999999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
-        <x:v>Yo-Chi Noosa</x:v>
+        <x:v>Yo-Chi Norwood</x:v>
       </x:c>
       <x:c r="B49" s="7" t="n">
-        <x:v>16846.22</x:v>
+        <x:v>13907.7</x:v>
       </x:c>
       <x:c r="C49" s="7" t="n">
-        <x:v>1791.92</x:v>
+        <x:v>2254.3</x:v>
       </x:c>
       <x:c r="D49" s="7" t="n">
-        <x:v>346770.82</x:v>
+        <x:v>293590.03</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>5.99</x:v>
       </x:c>
       <x:c r="F49" s="7" t="n">
-        <x:v>0.16999999999999998</x:v>
+        <x:v>0.53</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="str">
-        <x:v>Yo-Chi Norwood</x:v>
+        <x:v>Yo-Chi Paddington</x:v>
       </x:c>
       <x:c r="B50" s="7" t="n">
-        <x:v>13437.39</x:v>
+        <x:v>4709.54</x:v>
       </x:c>
       <x:c r="C50" s="7" t="n">
-        <x:v>2178.07</x:v>
+        <x:v>763.54</x:v>
       </x:c>
       <x:c r="D50" s="7" t="n">
-        <x:v>293590.03</x:v>
+        <x:v>277556.47</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
-        <x:v>5.99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F50" s="7" t="n">
-        <x:v>0.53</x:v>
+        <x:v>0.29</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
-        <x:v>Yo-Chi Paddington</x:v>
+        <x:v>Yo-Chi Penrith</x:v>
       </x:c>
       <x:c r="B51" s="7" t="n">
-        <x:v>4550.28</x:v>
+        <x:v>16171.8</x:v>
       </x:c>
       <x:c r="C51" s="7" t="n">
-        <x:v>737.72</x:v>
+        <x:v>1296.32</x:v>
       </x:c>
       <x:c r="D51" s="7" t="n">
-        <x:v>277556.47</x:v>
+        <x:v>322945.71</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="F51" s="7" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.27999999999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="str">
-        <x:v>Yo-Chi Penrith</x:v>
+        <x:v>Yo-Chi Prospect</x:v>
       </x:c>
       <x:c r="B52" s="7" t="n">
-        <x:v>15624.93</x:v>
+        <x:v>4197.5</x:v>
       </x:c>
       <x:c r="C52" s="7" t="n">
-        <x:v>1252.48</x:v>
+        <x:v>1581.38</x:v>
       </x:c>
       <x:c r="D52" s="7" t="n">
-        <x:v>322945.71</x:v>
+        <x:v>181118.27</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
-        <x:v>2.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F52" s="7" t="n">
-        <x:v>0.27999999999999997</x:v>
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="7" t="str">
-        <x:v>Yo-Chi Prospect</x:v>
+        <x:v>Yo-Chi QV</x:v>
       </x:c>
       <x:c r="B53" s="7" t="n">
-        <x:v>4055.56</x:v>
+        <x:v>11170.97</x:v>
       </x:c>
       <x:c r="C53" s="7" t="n">
-        <x:v>1527.9</x:v>
+        <x:v>996.23</x:v>
       </x:c>
       <x:c r="D53" s="7" t="n">
-        <x:v>181118.27</x:v>
+        <x:v>317915.66</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F53" s="7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.41000000000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="str">
-        <x:v>Yo-Chi QV</x:v>
+        <x:v>Yo-Chi Randwick</x:v>
       </x:c>
       <x:c r="B54" s="7" t="n">
-        <x:v>10793.21</x:v>
+        <x:v>4868.33</x:v>
       </x:c>
       <x:c r="C54" s="7" t="n">
-        <x:v>962.54</x:v>
+        <x:v>1657.65</x:v>
       </x:c>
       <x:c r="D54" s="7" t="n">
-        <x:v>317915.66</x:v>
+        <x:v>98016.59</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F54" s="7" t="n">
-        <x:v>0.41000000000000003</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="str">
-        <x:v>Yo-Chi Randwick</x:v>
+        <x:v>Yo-Chi Robina</x:v>
       </x:c>
       <x:c r="B55" s="7" t="n">
-        <x:v>4703.7</x:v>
+        <x:v>11391.9</x:v>
       </x:c>
       <x:c r="C55" s="7" t="n">
-        <x:v>1601.59</x:v>
+        <x:v>1889.62</x:v>
       </x:c>
       <x:c r="D55" s="7" t="n">
-        <x:v>98016.59</x:v>
+        <x:v>253273.15</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="F55" s="7" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.74</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7" t="str">
-        <x:v>Yo-Chi Robina</x:v>
+        <x:v>Yo-Chi Rouse Hill</x:v>
       </x:c>
       <x:c r="B56" s="7" t="n">
-        <x:v>11006.67</x:v>
+        <x:v>13251.93</x:v>
       </x:c>
       <x:c r="C56" s="7" t="n">
-        <x:v>1825.72</x:v>
+        <x:v>588.11</x:v>
       </x:c>
       <x:c r="D56" s="7" t="n">
-        <x:v>253273.15</x:v>
+        <x:v>202633.34</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>0.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F56" s="7" t="n">
-        <x:v>0.74</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="str">
-        <x:v>Yo-Chi Rouse Hill</x:v>
+        <x:v>Yo-Chi Semaphore</x:v>
       </x:c>
       <x:c r="B57" s="7" t="n">
-        <x:v>12803.8</x:v>
+        <x:v>7787.5</x:v>
       </x:c>
       <x:c r="C57" s="7" t="n">
-        <x:v>568.22</x:v>
+        <x:v>989.26</x:v>
       </x:c>
       <x:c r="D57" s="7" t="n">
-        <x:v>202633.34</x:v>
+        <x:v>273822.62</x:v>
       </x:c>
       <x:c r="E57" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F57" s="7" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.33</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="str">
-        <x:v>Yo-Chi Semaphore</x:v>
+        <x:v>Yo-Chi South Perth</x:v>
       </x:c>
       <x:c r="B58" s="7" t="n">
-        <x:v>7524.15</x:v>
+        <x:v>11292.3</x:v>
       </x:c>
       <x:c r="C58" s="7" t="n">
-        <x:v>955.81</x:v>
+        <x:v>2750.07</x:v>
       </x:c>
       <x:c r="D58" s="7" t="n">
-        <x:v>273822.62</x:v>
+        <x:v>292604.41</x:v>
       </x:c>
       <x:c r="E58" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="7" t="n">
-        <x:v>0.33</x:v>
+        <x:v>0.22</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="str">
-        <x:v>Yo-Chi South Perth</x:v>
+        <x:v>Yo-Chi Southbank</x:v>
       </x:c>
       <x:c r="B59" s="7" t="n">
-        <x:v>10910.43</x:v>
+        <x:v>1548.67</x:v>
       </x:c>
       <x:c r="C59" s="7" t="n">
-        <x:v>2657.07</x:v>
+        <x:v>185.76</x:v>
       </x:c>
       <x:c r="D59" s="7" t="n">
-        <x:v>292604.41</x:v>
+        <x:v>35020.65</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="7" t="n">
-        <x:v>0.22</x:v>
+        <x:v>2.13</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="str">
-        <x:v>Yo-Chi Southbank</x:v>
+        <x:v>Yo-Chi Southland</x:v>
       </x:c>
       <x:c r="B60" s="7" t="n">
-        <x:v>1496.3</x:v>
+        <x:v>11512.52</x:v>
       </x:c>
       <x:c r="C60" s="7" t="n">
-        <x:v>179.48</x:v>
+        <x:v>1093.14</x:v>
       </x:c>
       <x:c r="D60" s="7" t="n">
-        <x:v>35020.65</x:v>
+        <x:v>201509.47</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F60" s="7" t="n">
-        <x:v>2.13</x:v>
+        <x:v>0.6799999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="str">
-        <x:v>Yo-Chi Southland</x:v>
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
       </x:c>
       <x:c r="B61" s="7" t="n">
-        <x:v>11123.21</x:v>
+        <x:v>13485.16</x:v>
       </x:c>
       <x:c r="C61" s="7" t="n">
-        <x:v>1056.17</x:v>
+        <x:v>2654.74</x:v>
       </x:c>
       <x:c r="D61" s="7" t="n">
-        <x:v>201509.47</x:v>
+        <x:v>349920.3</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3.71</x:v>
       </x:c>
       <x:c r="F61" s="7" t="n">
-        <x:v>0.6799999999999999</x:v>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="str">
-        <x:v>Yo-Chi Sunshine Plaza</x:v>
+        <x:v>Yo-Chi Surry Hills</x:v>
       </x:c>
       <x:c r="B62" s="7" t="n">
-        <x:v>13029.14</x:v>
+        <x:v>20619.1</x:v>
       </x:c>
       <x:c r="C62" s="7" t="n">
-        <x:v>2564.97</x:v>
+        <x:v>69.48</x:v>
       </x:c>
       <x:c r="D62" s="7" t="n">
-        <x:v>349920.3</x:v>
+        <x:v>322260.55</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>3.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F62" s="7" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="7" t="str">
-        <x:v>Yo-Chi Surry Hills</x:v>
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
       </x:c>
       <x:c r="B63" s="7" t="n">
-        <x:v>19921.84</x:v>
+        <x:v>16165.83</x:v>
       </x:c>
       <x:c r="C63" s="7" t="n">
-        <x:v>67.13</x:v>
+        <x:v>4069.88</x:v>
       </x:c>
       <x:c r="D63" s="7" t="n">
-        <x:v>322260.55</x:v>
+        <x:v>342353.55</x:v>
       </x:c>
       <x:c r="E63" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="F63" s="7" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="str">
-        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
       </x:c>
       <x:c r="B64" s="7" t="n">
-        <x:v>15619.16</x:v>
+        <x:v>18747.31</x:v>
       </x:c>
       <x:c r="C64" s="7" t="n">
-        <x:v>3932.25</x:v>
+        <x:v>3590.38</x:v>
       </x:c>
       <x:c r="D64" s="7" t="n">
-        <x:v>342353.55</x:v>
+        <x:v>453063.94</x:v>
       </x:c>
       <x:c r="E64" s="7" t="n">
-        <x:v>2.01</x:v>
+        <x:v>1.78</x:v>
       </x:c>
       <x:c r="F64" s="7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.12</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="str">
-        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+        <x:v>Yo-Chi Top Ryde</x:v>
       </x:c>
       <x:c r="B65" s="7" t="n">
-        <x:v>18113.34</x:v>
+        <x:v>12601.08</x:v>
       </x:c>
       <x:c r="C65" s="7" t="n">
-        <x:v>3468.97</x:v>
+        <x:v>2917.04</x:v>
       </x:c>
       <x:c r="D65" s="7" t="n">
-        <x:v>453063.94</x:v>
+        <x:v>195101.37</x:v>
       </x:c>
       <x:c r="E65" s="7" t="n">
-        <x:v>1.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F65" s="7" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.61</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="str">
-        <x:v>Yo-Chi Top Ryde</x:v>
+        <x:v>Yo-Chi Vic Park</x:v>
       </x:c>
       <x:c r="B66" s="7" t="n">
-        <x:v>12174.96</x:v>
+        <x:v>5731.72</x:v>
       </x:c>
       <x:c r="C66" s="7" t="n">
-        <x:v>2818.4</x:v>
+        <x:v>1139.9</x:v>
       </x:c>
       <x:c r="D66" s="7" t="n">
-        <x:v>195101.37</x:v>
+        <x:v>368157.13</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F66" s="7" t="n">
-        <x:v>0.61</x:v>
+        <x:v>0.33</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="str">
-        <x:v>Yo-Chi Vic Park</x:v>
+        <x:v>Yo-Chi West End</x:v>
       </x:c>
       <x:c r="B67" s="7" t="n">
-        <x:v>5537.89</x:v>
+        <x:v>8739.84</x:v>
       </x:c>
       <x:c r="C67" s="7" t="n">
-        <x:v>1101.35</x:v>
+        <x:v>11.58</x:v>
       </x:c>
       <x:c r="D67" s="7" t="n">
-        <x:v>368157.13</x:v>
+        <x:v>230566.91</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F67" s="7" t="n">
-        <x:v>0.33</x:v>
+        <x:v>0.27</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="str">
-        <x:v>Yo-Chi West End</x:v>
+        <x:v>Yo-Chi Whitford City</x:v>
       </x:c>
       <x:c r="B68" s="7" t="n">
-        <x:v>8444.29</x:v>
+        <x:v>11613.47</x:v>
       </x:c>
       <x:c r="C68" s="7" t="n">
-        <x:v>11.19</x:v>
+        <x:v>1868.75</x:v>
       </x:c>
       <x:c r="D68" s="7" t="n">
-        <x:v>230566.91</x:v>
+        <x:v>274388.15</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="F68" s="7" t="n">
-        <x:v>0.27</x:v>
+        <x:v>0.27999999999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="str">
-        <x:v>Yo-Chi Whitford City</x:v>
+        <x:v>Yo-Chi Windsor</x:v>
       </x:c>
       <x:c r="B69" s="7" t="n">
-        <x:v>11220.74</x:v>
+        <x:v>9643.54</x:v>
       </x:c>
       <x:c r="C69" s="7" t="n">
-        <x:v>1805.56</x:v>
+        <x:v>1192.02</x:v>
       </x:c>
       <x:c r="D69" s="7" t="n">
-        <x:v>274388.15</x:v>
+        <x:v>206012.63</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
-        <x:v>2.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F69" s="7" t="n">
-        <x:v>0.27999999999999997</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="7" t="str">
-        <x:v>Yo-Chi Windsor</x:v>
-      </x:c>
-      <x:c r="B70" s="7" t="n">
-        <x:v>9317.43</x:v>
-      </x:c>
-      <x:c r="C70" s="7" t="n">
-        <x:v>1151.71</x:v>
-      </x:c>
-      <x:c r="D70" s="7" t="n">
-        <x:v>206012.63</x:v>
-      </x:c>
-      <x:c r="E70" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F70" s="7" t="n">
         <x:v>0.5499999999999999</x:v>
       </x:c>
     </x:row>
